--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="313" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1518427B-1D76-440B-AA07-68BC804DC315}"/>
+  <xr:revisionPtr revIDLastSave="327" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{490B3B1D-CC85-4033-A6B3-460AB38771C5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7333" uniqueCount="1170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7344" uniqueCount="1171">
   <si>
     <t>Client</t>
   </si>
@@ -3553,6 +3553,9 @@
   </si>
   <si>
     <t>BUVPN260158</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MONTAGE EXPLOITATION SERVICES</t>
   </si>
 </sst>
 </file>
@@ -4925,6 +4928,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -5242,7 +5249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W633"/>
+  <dimension ref="A1:W634"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.54296875" style="2" customWidth="1"/>
@@ -45008,7 +45015,7 @@
         <v>46265</v>
       </c>
       <c r="S589" s="8">
-        <f t="shared" ref="S589:S633" si="29">NETWORKDAYS(H589,R589)</f>
+        <f t="shared" ref="S589:S634" si="29">NETWORKDAYS(H589,R589)</f>
         <v>35</v>
       </c>
       <c r="T589" s="65" t="s">
@@ -46990,7 +46997,7 @@
         <v>46273</v>
       </c>
       <c r="J619" s="8">
-        <f t="shared" ref="J619:J633" si="30">+NETWORKDAYS(H619,I619)</f>
+        <f t="shared" ref="J619:J634" si="30">+NETWORKDAYS(H619,I619)</f>
         <v>8</v>
       </c>
       <c r="K619" s="17" t="s">
@@ -47964,6 +47971,73 @@
       </c>
       <c r="U633" s="65" t="s">
         <v>433</v>
+      </c>
+    </row>
+    <row r="634" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A634" s="17" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B634" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C634" s="17">
+        <v>67488775</v>
+      </c>
+      <c r="D634" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E634" s="17">
+        <v>2722580465</v>
+      </c>
+      <c r="F634" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G634" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H634" s="18">
+        <v>46233</v>
+      </c>
+      <c r="I634" s="18">
+        <v>46272</v>
+      </c>
+      <c r="J634" s="8">
+        <f t="shared" si="30"/>
+        <v>28</v>
+      </c>
+      <c r="K634" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L634" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M634" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N634" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="O634" s="65">
+        <v>150000</v>
+      </c>
+      <c r="P634" s="65">
+        <v>60000</v>
+      </c>
+      <c r="Q634" s="67">
+        <v>210000</v>
+      </c>
+      <c r="R634" s="66">
+        <v>46279</v>
+      </c>
+      <c r="S634" s="8">
+        <f t="shared" si="29"/>
+        <v>33</v>
+      </c>
+      <c r="T634" s="65" t="s">
+        <v>1154</v>
+      </c>
+      <c r="U634" s="65" t="s">
+        <v>537</v>
       </c>
     </row>
   </sheetData>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="327" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{490B3B1D-CC85-4033-A6B3-460AB38771C5}"/>
+  <xr:revisionPtr revIDLastSave="342" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFFC3568-E618-48BF-AE14-E7F23EC117A0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7344" uniqueCount="1171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7356" uniqueCount="1174">
   <si>
     <t>Client</t>
   </si>
@@ -3556,6 +3556,15 @@
   </si>
   <si>
     <t xml:space="preserve"> MONTAGE EXPLOITATION SERVICES</t>
+  </si>
+  <si>
+    <t>M'BAHAKRO</t>
+  </si>
+  <si>
+    <t>BUVPN260140</t>
+  </si>
+  <si>
+    <t>S38</t>
   </si>
 </sst>
 </file>
@@ -3569,7 +3578,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3673,6 +3682,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -3761,7 +3777,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3948,6 +3964,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -5249,7 +5278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W634"/>
+  <dimension ref="A1:W635"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.54296875" style="2" customWidth="1"/>
@@ -45015,7 +45044,7 @@
         <v>46265</v>
       </c>
       <c r="S589" s="8">
-        <f t="shared" ref="S589:S634" si="29">NETWORKDAYS(H589,R589)</f>
+        <f t="shared" ref="S589:S635" si="29">NETWORKDAYS(H589,R589)</f>
         <v>35</v>
       </c>
       <c r="T589" s="65" t="s">
@@ -46997,7 +47026,7 @@
         <v>46273</v>
       </c>
       <c r="J619" s="8">
-        <f t="shared" ref="J619:J634" si="30">+NETWORKDAYS(H619,I619)</f>
+        <f t="shared" ref="J619:J635" si="30">+NETWORKDAYS(H619,I619)</f>
         <v>8</v>
       </c>
       <c r="K619" s="17" t="s">
@@ -48034,10 +48063,77 @@
         <v>33</v>
       </c>
       <c r="T634" s="65" t="s">
-        <v>1154</v>
+        <v>1173</v>
       </c>
       <c r="U634" s="65" t="s">
         <v>537</v>
+      </c>
+    </row>
+    <row r="635" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A635" s="16" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B635" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C635" s="16">
+        <v>66523883</v>
+      </c>
+      <c r="D635" s="16" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E635" s="16" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F635" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G635" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H635" s="43">
+        <v>46217</v>
+      </c>
+      <c r="I635" s="43">
+        <v>46268</v>
+      </c>
+      <c r="J635" s="8">
+        <f t="shared" si="30"/>
+        <v>38</v>
+      </c>
+      <c r="K635" s="70" t="s">
+        <v>295</v>
+      </c>
+      <c r="L635" s="70" t="s">
+        <v>318</v>
+      </c>
+      <c r="M635" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="N635" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="O635" s="70">
+        <v>3500000</v>
+      </c>
+      <c r="P635" s="70">
+        <v>165000</v>
+      </c>
+      <c r="Q635" s="71">
+        <v>3665000</v>
+      </c>
+      <c r="R635" s="72">
+        <v>46279</v>
+      </c>
+      <c r="S635" s="8">
+        <f t="shared" si="29"/>
+        <v>45</v>
+      </c>
+      <c r="T635" s="73" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U635" s="74" t="s">
+        <v>433</v>
       </c>
     </row>
   </sheetData>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="342" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFFC3568-E618-48BF-AE14-E7F23EC117A0}"/>
+  <xr:revisionPtr revIDLastSave="360" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72592095-3B27-4DA8-AF03-D32EE9A91F5B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7356" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7367" uniqueCount="1174">
   <si>
     <t>Client</t>
   </si>
@@ -3578,7 +3578,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3688,6 +3688,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -3973,10 +3979,12 @@
     <xf numFmtId="14" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -5278,11 +5286,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W635"/>
+  <dimension ref="A1:W636"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.54296875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.90625" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" customWidth="1"/>
     <col min="4" max="4" width="16.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="11" style="5" bestFit="1" customWidth="1"/>
@@ -45044,7 +45052,7 @@
         <v>46265</v>
       </c>
       <c r="S589" s="8">
-        <f t="shared" ref="S589:S635" si="29">NETWORKDAYS(H589,R589)</f>
+        <f t="shared" ref="S589:S636" si="29">NETWORKDAYS(H589,R589)</f>
         <v>35</v>
       </c>
       <c r="T589" s="65" t="s">
@@ -47026,7 +47034,7 @@
         <v>46273</v>
       </c>
       <c r="J619" s="8">
-        <f t="shared" ref="J619:J635" si="30">+NETWORKDAYS(H619,I619)</f>
+        <f t="shared" ref="J619:J636" si="30">+NETWORKDAYS(H619,I619)</f>
         <v>8</v>
       </c>
       <c r="K619" s="17" t="s">
@@ -48070,31 +48078,31 @@
       </c>
     </row>
     <row r="635" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A635" s="16" t="s">
+      <c r="A635" s="17" t="s">
         <v>1103</v>
       </c>
-      <c r="B635" s="16" t="s">
+      <c r="B635" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C635" s="16">
+      <c r="C635" s="17">
         <v>66523883</v>
       </c>
-      <c r="D635" s="16" t="s">
+      <c r="D635" s="17" t="s">
         <v>1171</v>
       </c>
-      <c r="E635" s="16" t="s">
+      <c r="E635" s="17" t="s">
         <v>1172</v>
       </c>
-      <c r="F635" s="16" t="s">
+      <c r="F635" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="G635" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H635" s="43">
+      <c r="G635" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H635" s="18">
         <v>46217</v>
       </c>
-      <c r="I635" s="43">
+      <c r="I635" s="18">
         <v>46268</v>
       </c>
       <c r="J635" s="8">
@@ -48129,11 +48137,78 @@
         <f t="shared" si="29"/>
         <v>45</v>
       </c>
-      <c r="T635" s="73" t="s">
+      <c r="T635" s="65" t="s">
         <v>1173</v>
       </c>
-      <c r="U635" s="74" t="s">
+      <c r="U635" s="65" t="s">
         <v>433</v>
+      </c>
+    </row>
+    <row r="636" spans="1:21" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A636" s="73" t="s">
+        <v>701</v>
+      </c>
+      <c r="B636" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C636" s="73">
+        <v>69189192</v>
+      </c>
+      <c r="D636" s="73" t="s">
+        <v>479</v>
+      </c>
+      <c r="E636" s="73">
+        <v>2721387638</v>
+      </c>
+      <c r="F636" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="G636" s="73" t="s">
+        <v>23</v>
+      </c>
+      <c r="H636" s="74">
+        <v>46262</v>
+      </c>
+      <c r="I636" s="74">
+        <v>46265</v>
+      </c>
+      <c r="J636" s="8">
+        <f t="shared" si="30"/>
+        <v>2</v>
+      </c>
+      <c r="K636" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L636" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M636" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N636" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="O636" s="65">
+        <v>150000</v>
+      </c>
+      <c r="P636" s="65">
+        <v>40000</v>
+      </c>
+      <c r="Q636" s="67">
+        <v>190000</v>
+      </c>
+      <c r="R636" s="66">
+        <v>46279</v>
+      </c>
+      <c r="S636" s="8">
+        <f t="shared" si="29"/>
+        <v>12</v>
+      </c>
+      <c r="T636" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U636" s="65" t="s">
+        <v>537</v>
       </c>
     </row>
   </sheetData>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="360" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72592095-3B27-4DA8-AF03-D32EE9A91F5B}"/>
+  <xr:revisionPtr revIDLastSave="390" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16286856-D51F-4325-8991-207BCE5B9CD8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$613</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$642</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7367" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7437" uniqueCount="1185">
   <si>
     <t>Client</t>
   </si>
@@ -3565,6 +3565,39 @@
   </si>
   <si>
     <t>S38</t>
+  </si>
+  <si>
+    <t>CLINIQUE DES YEUX LASER</t>
+  </si>
+  <si>
+    <t>CORIS BANK</t>
+  </si>
+  <si>
+    <t>COCODY RIVIERA 3</t>
+  </si>
+  <si>
+    <t>BUVPN260152</t>
+  </si>
+  <si>
+    <t>OFFICE IVOIRIEN DES CHARGEURS</t>
+  </si>
+  <si>
+    <t>NOE</t>
+  </si>
+  <si>
+    <t>SYTHD260234</t>
+  </si>
+  <si>
+    <t>BUVPN260034</t>
+  </si>
+  <si>
+    <t>SOUDOTEC</t>
+  </si>
+  <si>
+    <t>MINIERE DE LA LOBO</t>
+  </si>
+  <si>
+    <t>SYTHD230030</t>
   </si>
 </sst>
 </file>
@@ -5286,7 +5319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W636"/>
+  <dimension ref="A1:W642"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.54296875" style="2" customWidth="1"/>
@@ -45052,7 +45085,7 @@
         <v>46265</v>
       </c>
       <c r="S589" s="8">
-        <f t="shared" ref="S589:S636" si="29">NETWORKDAYS(H589,R589)</f>
+        <f t="shared" ref="S589:S642" si="29">NETWORKDAYS(H589,R589)</f>
         <v>35</v>
       </c>
       <c r="T589" s="65" t="s">
@@ -47034,7 +47067,7 @@
         <v>46273</v>
       </c>
       <c r="J619" s="8">
-        <f t="shared" ref="J619:J636" si="30">+NETWORKDAYS(H619,I619)</f>
+        <f t="shared" ref="J619:J642" si="30">+NETWORKDAYS(H619,I619)</f>
         <v>8</v>
       </c>
       <c r="K619" s="17" t="s">
@@ -48079,130 +48112,130 @@
     </row>
     <row r="635" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A635" s="17" t="s">
-        <v>1103</v>
+        <v>1182</v>
       </c>
       <c r="B635" s="17" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C635" s="17">
-        <v>66523883</v>
+        <v>69135435</v>
       </c>
       <c r="D635" s="17" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E635" s="17" t="s">
-        <v>1172</v>
+        <v>49</v>
+      </c>
+      <c r="E635" s="17">
+        <v>2721354710</v>
       </c>
       <c r="F635" s="17" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G635" s="17" t="s">
         <v>23</v>
       </c>
       <c r="H635" s="18">
-        <v>46217</v>
+        <v>46261</v>
       </c>
       <c r="I635" s="18">
-        <v>46268</v>
+        <v>46279</v>
       </c>
       <c r="J635" s="8">
         <f t="shared" si="30"/>
-        <v>38</v>
-      </c>
-      <c r="K635" s="70" t="s">
-        <v>295</v>
-      </c>
-      <c r="L635" s="70" t="s">
-        <v>318</v>
-      </c>
-      <c r="M635" s="70" t="s">
-        <v>24</v>
-      </c>
-      <c r="N635" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="O635" s="70">
-        <v>3500000</v>
-      </c>
-      <c r="P635" s="70">
-        <v>165000</v>
-      </c>
-      <c r="Q635" s="71">
-        <v>3665000</v>
-      </c>
-      <c r="R635" s="72">
+        <v>13</v>
+      </c>
+      <c r="K635" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L635" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M635" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="N635" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="O635" s="65">
+        <v>150000</v>
+      </c>
+      <c r="P635" s="65">
+        <v>0</v>
+      </c>
+      <c r="Q635" s="67">
+        <v>150000</v>
+      </c>
+      <c r="R635" s="66">
         <v>46279</v>
       </c>
       <c r="S635" s="8">
         <f t="shared" si="29"/>
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="T635" s="65" t="s">
         <v>1173</v>
       </c>
       <c r="U635" s="65" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="636" spans="1:21" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.3">
-      <c r="A636" s="73" t="s">
-        <v>701</v>
-      </c>
-      <c r="B636" s="73" t="s">
-        <v>30</v>
-      </c>
-      <c r="C636" s="73">
-        <v>69189192</v>
-      </c>
-      <c r="D636" s="73" t="s">
-        <v>479</v>
-      </c>
-      <c r="E636" s="73">
-        <v>2721387638</v>
-      </c>
-      <c r="F636" s="73" t="s">
-        <v>32</v>
-      </c>
-      <c r="G636" s="73" t="s">
-        <v>23</v>
-      </c>
-      <c r="H636" s="74">
-        <v>46262</v>
-      </c>
-      <c r="I636" s="74">
-        <v>46265</v>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="636" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A636" s="17" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B636" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C636" s="17">
+        <v>67285588</v>
+      </c>
+      <c r="D636" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E636" s="17" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F636" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G636" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H636" s="18">
+        <v>46230</v>
+      </c>
+      <c r="I636" s="18">
+        <v>46279</v>
       </c>
       <c r="J636" s="8">
         <f t="shared" si="30"/>
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K636" s="65" t="s">
         <v>295</v>
       </c>
       <c r="L636" s="65" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M636" s="65" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="N636" s="65" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="O636" s="65">
-        <v>150000</v>
+        <v>850000</v>
       </c>
       <c r="P636" s="65">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="Q636" s="67">
-        <v>190000</v>
+        <v>850000</v>
       </c>
       <c r="R636" s="66">
         <v>46279</v>
       </c>
       <c r="S636" s="8">
         <f t="shared" si="29"/>
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="T636" s="65" t="s">
         <v>1173</v>
@@ -48211,28 +48244,430 @@
         <v>537</v>
       </c>
     </row>
+    <row r="637" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A637" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B637" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C637" s="17">
+        <v>66523883</v>
+      </c>
+      <c r="D637" s="17" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E637" s="17" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F637" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G637" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H637" s="18">
+        <v>46217</v>
+      </c>
+      <c r="I637" s="18">
+        <v>46268</v>
+      </c>
+      <c r="J637" s="8">
+        <f t="shared" si="30"/>
+        <v>38</v>
+      </c>
+      <c r="K637" s="70" t="s">
+        <v>295</v>
+      </c>
+      <c r="L637" s="70" t="s">
+        <v>318</v>
+      </c>
+      <c r="M637" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="N637" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="O637" s="70">
+        <v>3500000</v>
+      </c>
+      <c r="P637" s="70">
+        <v>165000</v>
+      </c>
+      <c r="Q637" s="71">
+        <v>3665000</v>
+      </c>
+      <c r="R637" s="72">
+        <v>46279</v>
+      </c>
+      <c r="S637" s="8">
+        <f t="shared" si="29"/>
+        <v>45</v>
+      </c>
+      <c r="T637" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U637" s="65" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="638" spans="1:21" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A638" s="73" t="s">
+        <v>701</v>
+      </c>
+      <c r="B638" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C638" s="73">
+        <v>69189192</v>
+      </c>
+      <c r="D638" s="73" t="s">
+        <v>479</v>
+      </c>
+      <c r="E638" s="73">
+        <v>2721387638</v>
+      </c>
+      <c r="F638" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="G638" s="73" t="s">
+        <v>23</v>
+      </c>
+      <c r="H638" s="74">
+        <v>46262</v>
+      </c>
+      <c r="I638" s="74">
+        <v>46265</v>
+      </c>
+      <c r="J638" s="8">
+        <f t="shared" si="30"/>
+        <v>2</v>
+      </c>
+      <c r="K638" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L638" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M638" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N638" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="O638" s="65">
+        <v>150000</v>
+      </c>
+      <c r="P638" s="65">
+        <v>40000</v>
+      </c>
+      <c r="Q638" s="67">
+        <v>190000</v>
+      </c>
+      <c r="R638" s="66">
+        <v>46279</v>
+      </c>
+      <c r="S638" s="8">
+        <f t="shared" si="29"/>
+        <v>12</v>
+      </c>
+      <c r="T638" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U638" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="639" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A639" s="17" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B639" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C639" s="17">
+        <v>65432145</v>
+      </c>
+      <c r="D639" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E639" s="17">
+        <v>2720257700</v>
+      </c>
+      <c r="F639" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G639" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H639" s="18">
+        <v>46197</v>
+      </c>
+      <c r="I639" s="18">
+        <v>46280</v>
+      </c>
+      <c r="J639" s="8">
+        <f t="shared" si="30"/>
+        <v>60</v>
+      </c>
+      <c r="K639" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L639" s="65" t="s">
+        <v>318</v>
+      </c>
+      <c r="M639" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N639" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="O639" s="65">
+        <v>1000000</v>
+      </c>
+      <c r="P639" s="65">
+        <v>495000</v>
+      </c>
+      <c r="Q639" s="67">
+        <v>1495000</v>
+      </c>
+      <c r="R639" s="66">
+        <v>46280</v>
+      </c>
+      <c r="S639" s="8">
+        <f t="shared" si="29"/>
+        <v>60</v>
+      </c>
+      <c r="T639" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U639" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="640" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A640" s="17" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B640" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C640" s="17">
+        <v>67777967</v>
+      </c>
+      <c r="D640" s="17" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E640" s="17" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F640" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G640" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H640" s="18">
+        <v>46238</v>
+      </c>
+      <c r="I640" s="18">
+        <v>46267</v>
+      </c>
+      <c r="J640" s="8">
+        <f t="shared" si="30"/>
+        <v>22</v>
+      </c>
+      <c r="K640" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L640" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M640" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N640" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="O640" s="65">
+        <v>500000</v>
+      </c>
+      <c r="P640" s="65">
+        <v>250000</v>
+      </c>
+      <c r="Q640" s="67">
+        <v>750000</v>
+      </c>
+      <c r="R640" s="66">
+        <v>46280</v>
+      </c>
+      <c r="S640" s="8">
+        <f t="shared" si="29"/>
+        <v>31</v>
+      </c>
+      <c r="T640" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U640" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="641" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A641" s="17" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B641" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C641" s="17">
+        <v>65800582</v>
+      </c>
+      <c r="D641" s="17" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E641" s="17" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F641" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G641" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H641" s="18">
+        <v>46205</v>
+      </c>
+      <c r="I641" s="18">
+        <v>46275</v>
+      </c>
+      <c r="J641" s="8">
+        <f t="shared" si="30"/>
+        <v>51</v>
+      </c>
+      <c r="K641" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L641" s="65" t="s">
+        <v>318</v>
+      </c>
+      <c r="M641" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N641" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="O641" s="65">
+        <v>100000</v>
+      </c>
+      <c r="P641" s="65">
+        <v>250000</v>
+      </c>
+      <c r="Q641" s="67">
+        <v>350000</v>
+      </c>
+      <c r="R641" s="66">
+        <v>46280</v>
+      </c>
+      <c r="S641" s="8">
+        <f t="shared" si="29"/>
+        <v>54</v>
+      </c>
+      <c r="T641" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U641" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="642" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A642" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="B642" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C642" s="17">
+        <v>56618123</v>
+      </c>
+      <c r="D642" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="E642" s="17" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F642" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G642" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H642" s="18">
+        <v>46035</v>
+      </c>
+      <c r="I642" s="18">
+        <v>46273</v>
+      </c>
+      <c r="J642" s="8">
+        <f t="shared" si="30"/>
+        <v>171</v>
+      </c>
+      <c r="K642" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L642" s="65" t="s">
+        <v>302</v>
+      </c>
+      <c r="M642" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N642" s="65" t="s">
+        <v>135</v>
+      </c>
+      <c r="O642" s="65">
+        <v>2000000</v>
+      </c>
+      <c r="P642" s="65">
+        <v>300000</v>
+      </c>
+      <c r="Q642" s="67">
+        <v>2300000</v>
+      </c>
+      <c r="R642" s="66">
+        <v>46281</v>
+      </c>
+      <c r="S642" s="8">
+        <f t="shared" si="29"/>
+        <v>177</v>
+      </c>
+      <c r="T642" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U642" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U613" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U642" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="C1">
     <cfRule type="duplicateValues" dxfId="95" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="93"/>
     <cfRule type="duplicateValues" dxfId="92" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C435 C444:C1048576">
     <cfRule type="duplicateValues" dxfId="89" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="85" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
     <cfRule type="duplicateValues" dxfId="83" priority="50"/>
@@ -48300,8 +48735,8 @@
     <cfRule type="duplicateValues" dxfId="61" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="60" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
     <cfRule type="duplicateValues" dxfId="58" priority="84"/>
@@ -48339,12 +48774,12 @@
     <cfRule type="duplicateValues" dxfId="46" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="45" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
     <cfRule type="duplicateValues" dxfId="41" priority="37"/>
@@ -48376,8 +48811,8 @@
     <cfRule type="duplicateValues" dxfId="31" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206">
-    <cfRule type="duplicateValues" dxfId="30" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
     <cfRule type="duplicateValues" dxfId="28" priority="21"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="390" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16286856-D51F-4325-8991-207BCE5B9CD8}"/>
+  <xr:revisionPtr revIDLastSave="412" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F081B410-FE97-47AB-A6FF-AB16DA07E8A4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$642</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$650</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7437" uniqueCount="1185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7530" uniqueCount="1198">
   <si>
     <t>Client</t>
   </si>
@@ -3598,6 +3598,45 @@
   </si>
   <si>
     <t>SYTHD230030</t>
+  </si>
+  <si>
+    <t>GESTOCI</t>
+  </si>
+  <si>
+    <t>SYTHD260247</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HUAWEI PROJET DOUANES INTELLIGENTES</t>
+  </si>
+  <si>
+    <t>ABOISSO&gt;&gt;&gt;PORT BOUET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYTHD260235 </t>
+  </si>
+  <si>
+    <t>SEMPA</t>
+  </si>
+  <si>
+    <t>SYTHD260250</t>
+  </si>
+  <si>
+    <t>AMBASSADE SUISSE</t>
+  </si>
+  <si>
+    <t>SYTHD260248</t>
+  </si>
+  <si>
+    <t>BUVPN260112</t>
+  </si>
+  <si>
+    <t>CFAO MOBILITY</t>
+  </si>
+  <si>
+    <t>OFFICE D'AIDE A LA COMMERCIALISATION DES PRODUITS VIVRIERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUMA HOSPITALITY </t>
   </si>
 </sst>
 </file>
@@ -4998,10 +5037,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -5319,7 +5354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W642"/>
+  <dimension ref="A1:W650"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.54296875" style="2" customWidth="1"/>
@@ -45085,7 +45120,7 @@
         <v>46265</v>
       </c>
       <c r="S589" s="8">
-        <f t="shared" ref="S589:S642" si="29">NETWORKDAYS(H589,R589)</f>
+        <f t="shared" ref="S589:S650" si="29">NETWORKDAYS(H589,R589)</f>
         <v>35</v>
       </c>
       <c r="T589" s="65" t="s">
@@ -47067,7 +47102,7 @@
         <v>46273</v>
       </c>
       <c r="J619" s="8">
-        <f t="shared" ref="J619:J642" si="30">+NETWORKDAYS(H619,I619)</f>
+        <f t="shared" ref="J619:J650" si="30">+NETWORKDAYS(H619,I619)</f>
         <v>8</v>
       </c>
       <c r="K619" s="17" t="s">
@@ -48646,28 +48681,564 @@
         <v>537</v>
       </c>
     </row>
+    <row r="643" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A643" s="17" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B643" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C643" s="17">
+        <v>69652230</v>
+      </c>
+      <c r="D643" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E643" s="17" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F643" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G643" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H643" s="18">
+        <v>46270</v>
+      </c>
+      <c r="I643" s="18">
+        <v>46280</v>
+      </c>
+      <c r="J643" s="8">
+        <f t="shared" si="30"/>
+        <v>7</v>
+      </c>
+      <c r="K643" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L643" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M643" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N643" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="O643" s="65">
+        <v>1000000</v>
+      </c>
+      <c r="P643" s="65">
+        <v>295767</v>
+      </c>
+      <c r="Q643" s="67">
+        <v>1295767</v>
+      </c>
+      <c r="R643" s="66">
+        <v>46281</v>
+      </c>
+      <c r="S643" s="8">
+        <f t="shared" si="29"/>
+        <v>8</v>
+      </c>
+      <c r="T643" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U643" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="644" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A644" s="17" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B644" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C644" s="17">
+        <v>69408141</v>
+      </c>
+      <c r="D644" s="17" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E644" s="17" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F644" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G644" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H644" s="18">
+        <v>46266</v>
+      </c>
+      <c r="I644" s="18">
+        <v>46272</v>
+      </c>
+      <c r="J644" s="8">
+        <f t="shared" si="30"/>
+        <v>5</v>
+      </c>
+      <c r="K644" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L644" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M644" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N644" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="O644" s="65">
+        <v>1259319</v>
+      </c>
+      <c r="P644" s="65">
+        <v>3291300</v>
+      </c>
+      <c r="Q644" s="67">
+        <v>4550619</v>
+      </c>
+      <c r="R644" s="66">
+        <v>46281</v>
+      </c>
+      <c r="S644" s="8">
+        <f t="shared" si="29"/>
+        <v>12</v>
+      </c>
+      <c r="T644" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U644" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="645" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A645" s="17" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B645" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C645" s="17">
+        <v>69121252</v>
+      </c>
+      <c r="D645" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E645" s="17" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F645" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G645" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H645" s="18">
+        <v>46261</v>
+      </c>
+      <c r="I645" s="18">
+        <v>46281</v>
+      </c>
+      <c r="J645" s="8">
+        <f t="shared" si="30"/>
+        <v>15</v>
+      </c>
+      <c r="K645" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L645" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M645" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N645" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="O645" s="65">
+        <v>875000</v>
+      </c>
+      <c r="P645" s="65">
+        <v>429000</v>
+      </c>
+      <c r="Q645" s="67">
+        <v>1304000</v>
+      </c>
+      <c r="R645" s="66">
+        <v>46281</v>
+      </c>
+      <c r="S645" s="8">
+        <f t="shared" si="29"/>
+        <v>15</v>
+      </c>
+      <c r="T645" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U645" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="646" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A646" s="17" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B646" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C646" s="17">
+        <v>69790474</v>
+      </c>
+      <c r="D646" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E646" s="17" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F646" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G646" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H646" s="18">
+        <v>46273</v>
+      </c>
+      <c r="I646" s="18">
+        <v>46282</v>
+      </c>
+      <c r="J646" s="8">
+        <f t="shared" si="30"/>
+        <v>8</v>
+      </c>
+      <c r="K646" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L646" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M646" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N646" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="O646" s="65">
+        <v>500000</v>
+      </c>
+      <c r="P646" s="65">
+        <v>284977</v>
+      </c>
+      <c r="Q646" s="67">
+        <v>784977</v>
+      </c>
+      <c r="R646" s="66">
+        <v>46282</v>
+      </c>
+      <c r="S646" s="8">
+        <f t="shared" si="29"/>
+        <v>8</v>
+      </c>
+      <c r="T646" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U646" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="647" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A647" s="17" t="s">
+        <v>928</v>
+      </c>
+      <c r="B647" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C647" s="17">
+        <v>65836320</v>
+      </c>
+      <c r="D647" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E647" s="17" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F647" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="G647" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H647" s="18">
+        <v>46205</v>
+      </c>
+      <c r="I647" s="18">
+        <v>46281</v>
+      </c>
+      <c r="J647" s="8">
+        <f t="shared" si="30"/>
+        <v>55</v>
+      </c>
+      <c r="K647" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L647" s="65" t="s">
+        <v>318</v>
+      </c>
+      <c r="M647" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N647" s="65" t="s">
+        <v>931</v>
+      </c>
+      <c r="O647" s="65">
+        <v>0</v>
+      </c>
+      <c r="P647" s="65">
+        <v>0</v>
+      </c>
+      <c r="Q647" s="67">
+        <v>0</v>
+      </c>
+      <c r="R647" s="66">
+        <v>46283</v>
+      </c>
+      <c r="S647" s="8">
+        <f t="shared" si="29"/>
+        <v>57</v>
+      </c>
+      <c r="T647" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U647" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="648" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A648" s="17" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B648" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C648" s="17">
+        <v>69803466</v>
+      </c>
+      <c r="D648" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E648" s="17">
+        <v>2721712324</v>
+      </c>
+      <c r="F648" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G648" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H648" s="18">
+        <v>46273</v>
+      </c>
+      <c r="I648" s="18">
+        <v>46283</v>
+      </c>
+      <c r="J648" s="8">
+        <f t="shared" si="30"/>
+        <v>9</v>
+      </c>
+      <c r="K648" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L648" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M648" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N648" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="O648" s="65">
+        <v>270000</v>
+      </c>
+      <c r="P648" s="65">
+        <v>71435</v>
+      </c>
+      <c r="Q648" s="67">
+        <v>341435</v>
+      </c>
+      <c r="R648" s="66">
+        <v>46283</v>
+      </c>
+      <c r="S648" s="8">
+        <f t="shared" si="29"/>
+        <v>9</v>
+      </c>
+      <c r="T648" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U648" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="649" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A649" s="17" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B649" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C649" s="17">
+        <v>69182973</v>
+      </c>
+      <c r="D649" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E649" s="17">
+        <v>2724391874</v>
+      </c>
+      <c r="F649" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G649" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H649" s="18">
+        <v>46262</v>
+      </c>
+      <c r="I649" s="18">
+        <v>46265</v>
+      </c>
+      <c r="J649" s="8">
+        <f t="shared" si="30"/>
+        <v>2</v>
+      </c>
+      <c r="K649" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L649" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M649" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N649" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="O649" s="65">
+        <v>150000</v>
+      </c>
+      <c r="P649" s="65">
+        <v>60000</v>
+      </c>
+      <c r="Q649" s="67">
+        <v>210000</v>
+      </c>
+      <c r="R649" s="66">
+        <v>46283</v>
+      </c>
+      <c r="S649" s="8">
+        <f t="shared" si="29"/>
+        <v>16</v>
+      </c>
+      <c r="T649" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U649" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="650" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A650" s="17" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B650" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C650" s="17">
+        <v>69190782</v>
+      </c>
+      <c r="D650" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E650" s="17">
+        <v>2722580500</v>
+      </c>
+      <c r="F650" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G650" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H650" s="18">
+        <v>46262</v>
+      </c>
+      <c r="I650" s="18">
+        <v>46281</v>
+      </c>
+      <c r="J650" s="8">
+        <f t="shared" si="30"/>
+        <v>14</v>
+      </c>
+      <c r="K650" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L650" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M650" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N650" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="O650" s="65">
+        <v>570000</v>
+      </c>
+      <c r="P650" s="65">
+        <v>221635</v>
+      </c>
+      <c r="Q650" s="67">
+        <v>791635</v>
+      </c>
+      <c r="R650" s="66">
+        <v>46283</v>
+      </c>
+      <c r="S650" s="8">
+        <f t="shared" si="29"/>
+        <v>16</v>
+      </c>
+      <c r="T650" s="65" t="s">
+        <v>1173</v>
+      </c>
+      <c r="U650" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U642" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U650" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="C1">
     <cfRule type="duplicateValues" dxfId="95" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="92"/>
     <cfRule type="duplicateValues" dxfId="92" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C435 C444:C1048576">
     <cfRule type="duplicateValues" dxfId="89" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="88" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="85" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
     <cfRule type="duplicateValues" dxfId="83" priority="50"/>
@@ -48735,8 +49306,8 @@
     <cfRule type="duplicateValues" dxfId="61" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="60" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
     <cfRule type="duplicateValues" dxfId="58" priority="84"/>
@@ -48774,12 +49345,12 @@
     <cfRule type="duplicateValues" dxfId="46" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="45" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="43" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
     <cfRule type="duplicateValues" dxfId="41" priority="37"/>
@@ -48811,8 +49382,8 @@
     <cfRule type="duplicateValues" dxfId="31" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206">
-    <cfRule type="duplicateValues" dxfId="30" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
     <cfRule type="duplicateValues" dxfId="28" priority="21"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="412" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F081B410-FE97-47AB-A6FF-AB16DA07E8A4}"/>
+  <xr:revisionPtr revIDLastSave="424" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F8A8F0A-7129-46C1-977C-1F80EB521D19}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7530" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7542" uniqueCount="1201">
   <si>
     <t>Client</t>
   </si>
@@ -3637,6 +3637,15 @@
   </si>
   <si>
     <t xml:space="preserve">LUMA HOSPITALITY </t>
+  </si>
+  <si>
+    <t>TINGRELA</t>
+  </si>
+  <si>
+    <t>BUVPN240192</t>
+  </si>
+  <si>
+    <t>S39</t>
   </si>
 </sst>
 </file>
@@ -3650,7 +3659,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3767,8 +3776,13 @@
       <name val="Aptos Display"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3796,6 +3810,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3855,7 +3875,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4057,6 +4077,22 @@
     <xf numFmtId="14" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -5354,7 +5390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W650"/>
+  <dimension ref="A1:W651"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.54296875" style="2" customWidth="1"/>
@@ -45120,7 +45156,7 @@
         <v>46265</v>
       </c>
       <c r="S589" s="8">
-        <f t="shared" ref="S589:S650" si="29">NETWORKDAYS(H589,R589)</f>
+        <f t="shared" ref="S589:S651" si="29">NETWORKDAYS(H589,R589)</f>
         <v>35</v>
       </c>
       <c r="T589" s="65" t="s">
@@ -47102,7 +47138,7 @@
         <v>46273</v>
       </c>
       <c r="J619" s="8">
-        <f t="shared" ref="J619:J650" si="30">+NETWORKDAYS(H619,I619)</f>
+        <f t="shared" ref="J619:J651" si="30">+NETWORKDAYS(H619,I619)</f>
         <v>8</v>
       </c>
       <c r="K619" s="17" t="s">
@@ -49214,6 +49250,74 @@
         <v>1173</v>
       </c>
       <c r="U650" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="651" spans="1:21" s="3" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A651" s="73" t="s">
+        <v>819</v>
+      </c>
+      <c r="B651" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="C651" s="73">
+        <v>69974913</v>
+      </c>
+      <c r="D651" s="75" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E651" s="73" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F651" s="75" t="s">
+        <v>46</v>
+      </c>
+      <c r="G651" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H651" s="74">
+        <v>46276</v>
+      </c>
+      <c r="I651" s="74">
+        <v>46283</v>
+      </c>
+      <c r="J651" s="8">
+        <f t="shared" si="30"/>
+        <v>6</v>
+      </c>
+      <c r="K651" s="76" t="s">
+        <v>295</v>
+      </c>
+      <c r="L651" s="75" t="s">
+        <v>296</v>
+      </c>
+      <c r="M651" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="N651" s="75" t="s">
+        <v>191</v>
+      </c>
+      <c r="O651" s="77">
+        <v>800000</v>
+      </c>
+      <c r="P651" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q651" s="77">
+        <f t="shared" ref="Q651" si="31">P651+O651</f>
+        <v>800000</v>
+      </c>
+      <c r="R651" s="78">
+        <v>46286</v>
+      </c>
+      <c r="S651" s="8">
+        <f t="shared" si="29"/>
+        <v>7</v>
+      </c>
+      <c r="T651" s="79" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U651" s="80" t="s">
         <v>537</v>
       </c>
     </row>
@@ -49222,23 +49326,23 @@
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="C1">
     <cfRule type="duplicateValues" dxfId="95" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="93"/>
     <cfRule type="duplicateValues" dxfId="92" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="96"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C435 C444:C1048576">
+  <conditionalFormatting sqref="C1:C435 C444:C650 C652:C1048576">
     <cfRule type="duplicateValues" dxfId="89" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="1"/>
+  <conditionalFormatting sqref="C1:C650 C652:C1048576">
+    <cfRule type="duplicateValues" dxfId="88" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="85" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
     <cfRule type="duplicateValues" dxfId="83" priority="50"/>
@@ -49306,8 +49410,8 @@
     <cfRule type="duplicateValues" dxfId="61" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="60" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
     <cfRule type="duplicateValues" dxfId="58" priority="84"/>
@@ -49345,12 +49449,12 @@
     <cfRule type="duplicateValues" dxfId="46" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="45" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
     <cfRule type="duplicateValues" dxfId="41" priority="37"/>
@@ -49382,8 +49486,8 @@
     <cfRule type="duplicateValues" dxfId="31" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206">
-    <cfRule type="duplicateValues" dxfId="30" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
     <cfRule type="duplicateValues" dxfId="28" priority="21"/>
@@ -49398,20 +49502,20 @@
   <conditionalFormatting sqref="C232:C242">
     <cfRule type="duplicateValues" dxfId="24" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C243:C286 C1:C204 C303:C328 C355:C356 C362:C369 C384:C395 C402:C435 C444:C1048576">
+  <conditionalFormatting sqref="C243:C286 C1:C204 C303:C328 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C1048576">
     <cfRule type="duplicateValues" dxfId="23" priority="184"/>
     <cfRule type="duplicateValues" dxfId="22" priority="185"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C243:C286 C1:C211 C303:C328 C355:C356 C362:C369 C384:C395 C402:C435 C444:C1048576">
+  <conditionalFormatting sqref="C243:C286 C1:C211 C303:C328 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C1048576">
     <cfRule type="duplicateValues" dxfId="21" priority="194"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C243:C286 C1:C231 C303:C328 C355:C356 C362:C369 C384:C395 C402:C435 C444:C1048576">
+  <conditionalFormatting sqref="C243:C286 C1:C231 C303:C328 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C1048576">
     <cfRule type="duplicateValues" dxfId="20" priority="199"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C303:C328 C1:C293 C355:C356 C362:C369 C384:C395 C402:C435 C444:C1048576">
+  <conditionalFormatting sqref="C303:C328 C1:C293 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C1048576">
     <cfRule type="duplicateValues" dxfId="19" priority="204"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C303:C328 C1:C294 C355:C356 C362:C369 C384:C395 C402:C435 C444:C1048576">
+  <conditionalFormatting sqref="C303:C328 C1:C294 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C1048576">
     <cfRule type="duplicateValues" dxfId="18" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C340:C346">
@@ -49423,10 +49527,10 @@
   <conditionalFormatting sqref="C383">
     <cfRule type="duplicateValues" dxfId="15" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C384:C395 C1:C369 C402:C435 C444:C1048576">
+  <conditionalFormatting sqref="C384:C395 C1:C369 C402:C435 C444:C650 C652:C1048576">
     <cfRule type="duplicateValues" dxfId="14" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C402:C435 C1:C395 C444:C1048576">
+  <conditionalFormatting sqref="C402:C435 C1:C395 C444:C650 C652:C1048576">
     <cfRule type="duplicateValues" dxfId="13" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="424" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F8A8F0A-7129-46C1-977C-1F80EB521D19}"/>
+  <xr:revisionPtr revIDLastSave="444" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0603A00-E34D-489A-AA8C-5577E7BCC5BB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$650</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$665</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7542" uniqueCount="1201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7705" uniqueCount="1221">
   <si>
     <t>Client</t>
   </si>
@@ -3646,6 +3646,66 @@
   </si>
   <si>
     <t>S39</t>
+  </si>
+  <si>
+    <t>EDJDSD</t>
+  </si>
+  <si>
+    <t>SYTHD260245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYTHD260251 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRIDGE BANK GRAND-BASSAM </t>
+  </si>
+  <si>
+    <t>LUMA HOSPITALITY</t>
+  </si>
+  <si>
+    <t>SYTHD260246</t>
+  </si>
+  <si>
+    <t>CYBASTION</t>
+  </si>
+  <si>
+    <t>SYTHD260253</t>
+  </si>
+  <si>
+    <t>BANQUE MONDIALE</t>
+  </si>
+  <si>
+    <t>SYTHD260258</t>
+  </si>
+  <si>
+    <t>SYTHD220206</t>
+  </si>
+  <si>
+    <t>DAOUKRO</t>
+  </si>
+  <si>
+    <t>BUVPN260116</t>
+  </si>
+  <si>
+    <t>KEDA COTE D'IVOIRE CERAMICS</t>
+  </si>
+  <si>
+    <t>ALEPE</t>
+  </si>
+  <si>
+    <t>SYTHD260243</t>
+  </si>
+  <si>
+    <t>CACAO ET COSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EDJDSD </t>
+  </si>
+  <si>
+    <t>SYTHD260244</t>
+  </si>
+  <si>
+    <t>CNAM</t>
   </si>
 </sst>
 </file>
@@ -3875,7 +3935,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4088,9 +4148,6 @@
     </xf>
     <xf numFmtId="14" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -5390,7 +5447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W651"/>
+  <dimension ref="A1:W665"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.54296875" style="2" customWidth="1"/>
@@ -45156,7 +45213,7 @@
         <v>46265</v>
       </c>
       <c r="S589" s="8">
-        <f t="shared" ref="S589:S651" si="29">NETWORKDAYS(H589,R589)</f>
+        <f t="shared" ref="S589:S652" si="29">NETWORKDAYS(H589,R589)</f>
         <v>35</v>
       </c>
       <c r="T589" s="65" t="s">
@@ -47138,7 +47195,7 @@
         <v>46273</v>
       </c>
       <c r="J619" s="8">
-        <f t="shared" ref="J619:J651" si="30">+NETWORKDAYS(H619,I619)</f>
+        <f t="shared" ref="J619:J665" si="30">+NETWORKDAYS(H619,I619)</f>
         <v>8</v>
       </c>
       <c r="K619" s="17" t="s">
@@ -49314,35 +49371,973 @@
         <f t="shared" si="29"/>
         <v>7</v>
       </c>
-      <c r="T651" s="79" t="s">
+      <c r="T651" s="65" t="s">
         <v>1200</v>
       </c>
-      <c r="U651" s="80" t="s">
+      <c r="U651" s="79" t="s">
         <v>537</v>
       </c>
     </row>
+    <row r="652" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A652" s="17" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B652" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C652" s="17">
+        <v>68272822</v>
+      </c>
+      <c r="D652" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E652" s="17" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F652" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G652" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H652" s="18">
+        <v>46247</v>
+      </c>
+      <c r="I652" s="18">
+        <v>46281</v>
+      </c>
+      <c r="J652" s="8">
+        <f t="shared" si="30"/>
+        <v>25</v>
+      </c>
+      <c r="K652" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L652" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M652" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N652" s="65" t="s">
+        <v>262</v>
+      </c>
+      <c r="O652" s="65">
+        <v>2000000</v>
+      </c>
+      <c r="P652" s="65">
+        <v>215000</v>
+      </c>
+      <c r="Q652" s="67">
+        <v>2215000</v>
+      </c>
+      <c r="R652" s="66">
+        <v>46286</v>
+      </c>
+      <c r="S652" s="8">
+        <f t="shared" si="29"/>
+        <v>28</v>
+      </c>
+      <c r="T652" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U652" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="653" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A653" s="17" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B653" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C653" s="17">
+        <v>67062562</v>
+      </c>
+      <c r="D653" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E653" s="17" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F653" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G653" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H653" s="18">
+        <v>46226</v>
+      </c>
+      <c r="I653" s="18">
+        <v>46282</v>
+      </c>
+      <c r="J653" s="8">
+        <f t="shared" si="30"/>
+        <v>41</v>
+      </c>
+      <c r="K653" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L653" s="65" t="s">
+        <v>318</v>
+      </c>
+      <c r="M653" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N653" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="O653" s="65">
+        <v>500000</v>
+      </c>
+      <c r="P653" s="65">
+        <v>850000</v>
+      </c>
+      <c r="Q653" s="67">
+        <v>1350000</v>
+      </c>
+      <c r="R653" s="66">
+        <v>46286</v>
+      </c>
+      <c r="S653" s="8">
+        <f t="shared" ref="S653:S665" si="32">NETWORKDAYS(H653,R653)</f>
+        <v>43</v>
+      </c>
+      <c r="T653" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U653" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="654" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A654" s="17" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B654" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C654" s="17">
+        <v>64761746</v>
+      </c>
+      <c r="D654" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E654" s="17">
+        <v>2721712170</v>
+      </c>
+      <c r="F654" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G654" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H654" s="18">
+        <v>46185</v>
+      </c>
+      <c r="I654" s="18">
+        <v>46286</v>
+      </c>
+      <c r="J654" s="8">
+        <f t="shared" si="30"/>
+        <v>72</v>
+      </c>
+      <c r="K654" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L654" s="65" t="s">
+        <v>318</v>
+      </c>
+      <c r="M654" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N654" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="O654" s="65">
+        <v>150000</v>
+      </c>
+      <c r="P654" s="65">
+        <v>60000</v>
+      </c>
+      <c r="Q654" s="67">
+        <v>210000</v>
+      </c>
+      <c r="R654" s="66">
+        <v>46286</v>
+      </c>
+      <c r="S654" s="8">
+        <f t="shared" si="32"/>
+        <v>72</v>
+      </c>
+      <c r="T654" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U654" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="655" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A655" s="17" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B655" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C655" s="17">
+        <v>69173063</v>
+      </c>
+      <c r="D655" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E655" s="17" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F655" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G655" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H655" s="18">
+        <v>46262</v>
+      </c>
+      <c r="I655" s="18">
+        <v>46281</v>
+      </c>
+      <c r="J655" s="8">
+        <f t="shared" si="30"/>
+        <v>14</v>
+      </c>
+      <c r="K655" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L655" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M655" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N655" s="65" t="s">
+        <v>262</v>
+      </c>
+      <c r="O655" s="65">
+        <v>2000000</v>
+      </c>
+      <c r="P655" s="65">
+        <v>484889</v>
+      </c>
+      <c r="Q655" s="67">
+        <v>2484889</v>
+      </c>
+      <c r="R655" s="66">
+        <v>46287</v>
+      </c>
+      <c r="S655" s="8">
+        <f t="shared" si="32"/>
+        <v>18</v>
+      </c>
+      <c r="T655" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U655" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="656" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A656" s="17" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B656" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C656" s="17">
+        <v>70270437</v>
+      </c>
+      <c r="D656" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E656" s="17" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F656" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G656" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H656" s="18">
+        <v>46281</v>
+      </c>
+      <c r="I656" s="18">
+        <v>46283</v>
+      </c>
+      <c r="J656" s="8">
+        <f t="shared" si="30"/>
+        <v>3</v>
+      </c>
+      <c r="K656" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L656" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M656" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N656" s="65" t="s">
+        <v>254</v>
+      </c>
+      <c r="O656" s="65">
+        <v>2508676</v>
+      </c>
+      <c r="P656" s="65">
+        <v>1000219</v>
+      </c>
+      <c r="Q656" s="67">
+        <v>3508895</v>
+      </c>
+      <c r="R656" s="66">
+        <v>46287</v>
+      </c>
+      <c r="S656" s="8">
+        <f t="shared" si="32"/>
+        <v>5</v>
+      </c>
+      <c r="T656" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U656" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="657" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A657" s="17" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B657" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C657" s="17">
+        <v>70424921</v>
+      </c>
+      <c r="D657" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E657" s="17" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F657" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G657" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H657" s="18">
+        <v>46283</v>
+      </c>
+      <c r="I657" s="18">
+        <v>46286</v>
+      </c>
+      <c r="J657" s="8">
+        <f t="shared" si="30"/>
+        <v>2</v>
+      </c>
+      <c r="K657" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L657" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M657" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N657" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="O657" s="65">
+        <v>1605954</v>
+      </c>
+      <c r="P657" s="65">
+        <v>0</v>
+      </c>
+      <c r="Q657" s="67">
+        <v>1605954</v>
+      </c>
+      <c r="R657" s="66">
+        <v>46286</v>
+      </c>
+      <c r="S657" s="8">
+        <f t="shared" si="32"/>
+        <v>2</v>
+      </c>
+      <c r="T657" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U657" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="658" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A658" s="17" t="s">
+        <v>766</v>
+      </c>
+      <c r="B658" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C658" s="17">
+        <v>60757807</v>
+      </c>
+      <c r="D658" s="17" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E658" s="17">
+        <v>2720242424</v>
+      </c>
+      <c r="F658" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G658" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H658" s="18">
+        <v>46111</v>
+      </c>
+      <c r="I658" s="18">
+        <v>46251</v>
+      </c>
+      <c r="J658" s="8">
+        <f t="shared" si="30"/>
+        <v>101</v>
+      </c>
+      <c r="K658" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L658" s="65" t="s">
+        <v>302</v>
+      </c>
+      <c r="M658" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="N658" s="65" t="s">
+        <v>82</v>
+      </c>
+      <c r="O658" s="65">
+        <v>1000000</v>
+      </c>
+      <c r="P658" s="65">
+        <v>0</v>
+      </c>
+      <c r="Q658" s="67">
+        <v>1000000</v>
+      </c>
+      <c r="R658" s="66">
+        <v>46287</v>
+      </c>
+      <c r="S658" s="8">
+        <f t="shared" si="32"/>
+        <v>127</v>
+      </c>
+      <c r="T658" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U658" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="659" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A659" s="17" t="s">
+        <v>766</v>
+      </c>
+      <c r="B659" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C659" s="17">
+        <v>60747953</v>
+      </c>
+      <c r="D659" s="17" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E659" s="17">
+        <v>2720201600</v>
+      </c>
+      <c r="F659" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G659" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H659" s="18">
+        <v>46111</v>
+      </c>
+      <c r="I659" s="18">
+        <v>46253</v>
+      </c>
+      <c r="J659" s="8">
+        <f t="shared" si="30"/>
+        <v>103</v>
+      </c>
+      <c r="K659" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L659" s="65" t="s">
+        <v>302</v>
+      </c>
+      <c r="M659" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="N659" s="65" t="s">
+        <v>82</v>
+      </c>
+      <c r="O659" s="65">
+        <v>1000000</v>
+      </c>
+      <c r="P659" s="65">
+        <v>0</v>
+      </c>
+      <c r="Q659" s="67">
+        <v>1000000</v>
+      </c>
+      <c r="R659" s="66">
+        <v>46287</v>
+      </c>
+      <c r="S659" s="8">
+        <f t="shared" si="32"/>
+        <v>127</v>
+      </c>
+      <c r="T659" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U659" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="660" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A660" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="B660" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C660" s="17">
+        <v>66190079</v>
+      </c>
+      <c r="D660" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E660" s="17" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F660" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G660" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H660" s="18">
+        <v>46211</v>
+      </c>
+      <c r="I660" s="18">
+        <v>46275</v>
+      </c>
+      <c r="J660" s="8">
+        <f t="shared" si="30"/>
+        <v>47</v>
+      </c>
+      <c r="K660" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L660" s="65" t="s">
+        <v>302</v>
+      </c>
+      <c r="M660" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="N660" s="65" t="s">
+        <v>103</v>
+      </c>
+      <c r="O660" s="65">
+        <v>500000</v>
+      </c>
+      <c r="P660" s="65">
+        <v>0</v>
+      </c>
+      <c r="Q660" s="67">
+        <v>500000</v>
+      </c>
+      <c r="R660" s="66">
+        <v>46287</v>
+      </c>
+      <c r="S660" s="8">
+        <f t="shared" si="32"/>
+        <v>55</v>
+      </c>
+      <c r="T660" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U660" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="661" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A661" s="17" t="s">
+        <v>928</v>
+      </c>
+      <c r="B661" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C661" s="17">
+        <v>65833190</v>
+      </c>
+      <c r="D661" s="17" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E661" s="17" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F661" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="G661" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H661" s="18">
+        <v>46205</v>
+      </c>
+      <c r="I661" s="18">
+        <v>46286</v>
+      </c>
+      <c r="J661" s="8">
+        <f t="shared" si="30"/>
+        <v>58</v>
+      </c>
+      <c r="K661" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L661" s="65" t="s">
+        <v>318</v>
+      </c>
+      <c r="M661" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N661" s="65" t="s">
+        <v>931</v>
+      </c>
+      <c r="O661" s="65">
+        <v>0</v>
+      </c>
+      <c r="P661" s="65">
+        <v>0</v>
+      </c>
+      <c r="Q661" s="67">
+        <v>0</v>
+      </c>
+      <c r="R661" s="66">
+        <v>46287</v>
+      </c>
+      <c r="S661" s="8">
+        <f t="shared" si="32"/>
+        <v>59</v>
+      </c>
+      <c r="T661" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U661" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="662" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A662" s="17" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B662" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C662" s="17">
+        <v>69372201</v>
+      </c>
+      <c r="D662" s="17" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E662" s="17" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F662" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="G662" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H662" s="18">
+        <v>46266</v>
+      </c>
+      <c r="I662" s="18">
+        <v>46286</v>
+      </c>
+      <c r="J662" s="8">
+        <f t="shared" si="30"/>
+        <v>15</v>
+      </c>
+      <c r="K662" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L662" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M662" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N662" s="65" t="s">
+        <v>262</v>
+      </c>
+      <c r="O662" s="65">
+        <v>1386000</v>
+      </c>
+      <c r="P662" s="65">
+        <v>107800</v>
+      </c>
+      <c r="Q662" s="67">
+        <v>1493800</v>
+      </c>
+      <c r="R662" s="66">
+        <v>46287</v>
+      </c>
+      <c r="S662" s="8">
+        <f t="shared" si="32"/>
+        <v>16</v>
+      </c>
+      <c r="T662" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U662" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="663" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A663" s="17" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B663" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C663" s="17">
+        <v>66962325</v>
+      </c>
+      <c r="D663" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E663" s="17">
+        <v>2721712313</v>
+      </c>
+      <c r="F663" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G663" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H663" s="18">
+        <v>46224</v>
+      </c>
+      <c r="I663" s="18">
+        <v>46282</v>
+      </c>
+      <c r="J663" s="8">
+        <f t="shared" si="30"/>
+        <v>43</v>
+      </c>
+      <c r="K663" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L663" s="65" t="s">
+        <v>318</v>
+      </c>
+      <c r="M663" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N663" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="O663" s="65">
+        <v>270000</v>
+      </c>
+      <c r="P663" s="65">
+        <v>111435</v>
+      </c>
+      <c r="Q663" s="67">
+        <v>381435</v>
+      </c>
+      <c r="R663" s="66">
+        <v>46287</v>
+      </c>
+      <c r="S663" s="8">
+        <f t="shared" si="32"/>
+        <v>46</v>
+      </c>
+      <c r="T663" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U663" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="664" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A664" s="17" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B664" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C664" s="17">
+        <v>68272847</v>
+      </c>
+      <c r="D664" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E664" s="17" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F664" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G664" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="H664" s="18">
+        <v>46247</v>
+      </c>
+      <c r="I664" s="18">
+        <v>46287</v>
+      </c>
+      <c r="J664" s="8">
+        <f t="shared" si="30"/>
+        <v>29</v>
+      </c>
+      <c r="K664" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L664" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M664" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N664" s="65" t="s">
+        <v>262</v>
+      </c>
+      <c r="O664" s="65">
+        <v>2000000</v>
+      </c>
+      <c r="P664" s="65">
+        <v>815000</v>
+      </c>
+      <c r="Q664" s="67">
+        <v>2815000</v>
+      </c>
+      <c r="R664" s="66">
+        <v>46288</v>
+      </c>
+      <c r="S664" s="8">
+        <f t="shared" si="32"/>
+        <v>30</v>
+      </c>
+      <c r="T664" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U664" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="665" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A665" s="17" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B665" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C665" s="17">
+        <v>69451554</v>
+      </c>
+      <c r="D665" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E665" s="17">
+        <v>2720253939</v>
+      </c>
+      <c r="F665" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G665" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H665" s="18">
+        <v>46267</v>
+      </c>
+      <c r="I665" s="18">
+        <v>46286</v>
+      </c>
+      <c r="J665" s="8">
+        <f t="shared" si="30"/>
+        <v>14</v>
+      </c>
+      <c r="K665" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L665" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M665" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N665" s="65" t="s">
+        <v>82</v>
+      </c>
+      <c r="O665" s="65">
+        <v>0</v>
+      </c>
+      <c r="P665" s="65">
+        <v>0</v>
+      </c>
+      <c r="Q665" s="67">
+        <v>0</v>
+      </c>
+      <c r="R665" s="66">
+        <v>46288</v>
+      </c>
+      <c r="S665" s="8">
+        <f t="shared" si="32"/>
+        <v>16</v>
+      </c>
+      <c r="T665" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U665" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U650" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U665" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="C1">
     <cfRule type="duplicateValues" dxfId="95" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="92"/>
     <cfRule type="duplicateValues" dxfId="92" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C435 C444:C650 C652:C1048576">
     <cfRule type="duplicateValues" dxfId="89" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C650 C652:C1048576">
-    <cfRule type="duplicateValues" dxfId="88" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C15 C17:C31">
-    <cfRule type="duplicateValues" dxfId="85" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C58">
     <cfRule type="duplicateValues" dxfId="83" priority="50"/>
@@ -49410,8 +50405,8 @@
     <cfRule type="duplicateValues" dxfId="61" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="60" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
     <cfRule type="duplicateValues" dxfId="58" priority="84"/>
@@ -49449,12 +50444,12 @@
     <cfRule type="duplicateValues" dxfId="46" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166">
-    <cfRule type="duplicateValues" dxfId="45" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C167">
-    <cfRule type="duplicateValues" dxfId="43" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C168">
     <cfRule type="duplicateValues" dxfId="41" priority="37"/>
@@ -49486,8 +50481,8 @@
     <cfRule type="duplicateValues" dxfId="31" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C206">
-    <cfRule type="duplicateValues" dxfId="30" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C207">
     <cfRule type="duplicateValues" dxfId="28" priority="21"/>

--- a/Input.xlsx
+++ b/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="444" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0603A00-E34D-489A-AA8C-5577E7BCC5BB}"/>
+  <xr:revisionPtr revIDLastSave="475" documentId="11_26573A825B844769D80B0CAB0943EC1510201055" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A43CEFC-AC7C-44A4-9762-5BDAA8453B09}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MES" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$665</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MES!$A$1:$U$673</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7705" uniqueCount="1221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7811" uniqueCount="1233">
   <si>
     <t>Client</t>
   </si>
@@ -3706,6 +3706,42 @@
   </si>
   <si>
     <t>CNAM</t>
+  </si>
+  <si>
+    <t>COMPAGNIE GENERALE DE FINANCE ET DE GESTION</t>
+  </si>
+  <si>
+    <t>SYTHD260255</t>
+  </si>
+  <si>
+    <t>NESTLE COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>SYTHD260252</t>
+  </si>
+  <si>
+    <t>MUGEF CI</t>
+  </si>
+  <si>
+    <t>BUVPN260117</t>
+  </si>
+  <si>
+    <t>GAUFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-CONSEILS COCODY </t>
+  </si>
+  <si>
+    <t>BUVPN260162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUVPN260167 </t>
+  </si>
+  <si>
+    <t>BUVPN260115</t>
+  </si>
+  <si>
+    <t>BUVPN260166</t>
   </si>
 </sst>
 </file>
@@ -3719,7 +3755,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3841,6 +3877,12 @@
       <name val="Aptos Display"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -3935,7 +3977,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4150,6 +4192,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -5447,7 +5495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W665"/>
+  <dimension ref="A1:W674"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.54296875" style="2" customWidth="1"/>
@@ -47195,7 +47243,7 @@
         <v>46273</v>
       </c>
       <c r="J619" s="8">
-        <f t="shared" ref="J619:J665" si="30">+NETWORKDAYS(H619,I619)</f>
+        <f t="shared" ref="J619:J674" si="30">+NETWORKDAYS(H619,I619)</f>
         <v>8</v>
       </c>
       <c r="K619" s="17" t="s">
@@ -49502,7 +49550,7 @@
         <v>46286</v>
       </c>
       <c r="S653" s="8">
-        <f t="shared" ref="S653:S665" si="32">NETWORKDAYS(H653,R653)</f>
+        <f t="shared" ref="S653:S674" si="32">NETWORKDAYS(H653,R653)</f>
         <v>43</v>
       </c>
       <c r="T653" s="65" t="s">
@@ -50316,8 +50364,612 @@
         <v>537</v>
       </c>
     </row>
+    <row r="666" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A666" s="17" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B666" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C666" s="17">
+        <v>69434883</v>
+      </c>
+      <c r="D666" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E666" s="17" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F666" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G666" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H666" s="18">
+        <v>46267</v>
+      </c>
+      <c r="I666" s="18">
+        <v>46289</v>
+      </c>
+      <c r="J666" s="8">
+        <f t="shared" si="30"/>
+        <v>17</v>
+      </c>
+      <c r="K666" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L666" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M666" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N666" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="O666" s="65">
+        <v>1480307</v>
+      </c>
+      <c r="P666" s="65">
+        <v>566051</v>
+      </c>
+      <c r="Q666" s="67">
+        <v>2046358</v>
+      </c>
+      <c r="R666" s="66">
+        <v>46289</v>
+      </c>
+      <c r="S666" s="8">
+        <f t="shared" si="32"/>
+        <v>17</v>
+      </c>
+      <c r="T666" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U666" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="667" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A667" s="17" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B667" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C667" s="17">
+        <v>69529704</v>
+      </c>
+      <c r="D667" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E667" s="17" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F667" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G667" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H667" s="18">
+        <v>46268</v>
+      </c>
+      <c r="I667" s="18">
+        <v>46289</v>
+      </c>
+      <c r="J667" s="8">
+        <f t="shared" si="30"/>
+        <v>16</v>
+      </c>
+      <c r="K667" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L667" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M667" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N667" s="65" t="s">
+        <v>92</v>
+      </c>
+      <c r="O667" s="65">
+        <v>1000000</v>
+      </c>
+      <c r="P667" s="65">
+        <v>1850000</v>
+      </c>
+      <c r="Q667" s="67">
+        <v>2850000</v>
+      </c>
+      <c r="R667" s="66">
+        <v>46289</v>
+      </c>
+      <c r="S667" s="8">
+        <f t="shared" si="32"/>
+        <v>16</v>
+      </c>
+      <c r="T667" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U667" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="668" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A668" s="17" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B668" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C668" s="17">
+        <v>65828465</v>
+      </c>
+      <c r="D668" s="17" t="s">
+        <v>604</v>
+      </c>
+      <c r="E668" s="17" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F668" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="G668" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H668" s="18">
+        <v>46205</v>
+      </c>
+      <c r="I668" s="18">
+        <v>46274</v>
+      </c>
+      <c r="J668" s="8">
+        <f t="shared" si="30"/>
+        <v>50</v>
+      </c>
+      <c r="K668" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L668" s="65" t="s">
+        <v>318</v>
+      </c>
+      <c r="M668" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N668" s="65" t="s">
+        <v>931</v>
+      </c>
+      <c r="O668" s="65">
+        <v>0</v>
+      </c>
+      <c r="P668" s="65">
+        <v>0</v>
+      </c>
+      <c r="Q668" s="67">
+        <v>0</v>
+      </c>
+      <c r="R668" s="66">
+        <v>46289</v>
+      </c>
+      <c r="S668" s="8">
+        <f t="shared" si="32"/>
+        <v>61</v>
+      </c>
+      <c r="T668" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U668" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="669" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A669" s="17" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B669" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C669" s="17">
+        <v>70404284</v>
+      </c>
+      <c r="D669" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E669" s="17">
+        <v>2722221300</v>
+      </c>
+      <c r="F669" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G669" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H669" s="18">
+        <v>46283</v>
+      </c>
+      <c r="I669" s="18">
+        <v>46288</v>
+      </c>
+      <c r="J669" s="8">
+        <f t="shared" si="30"/>
+        <v>4</v>
+      </c>
+      <c r="K669" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L669" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="M669" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N669" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="O669" s="65">
+        <v>150000</v>
+      </c>
+      <c r="P669" s="65">
+        <v>40000</v>
+      </c>
+      <c r="Q669" s="67">
+        <v>190000</v>
+      </c>
+      <c r="R669" s="66">
+        <v>46289</v>
+      </c>
+      <c r="S669" s="8">
+        <f t="shared" si="32"/>
+        <v>5</v>
+      </c>
+      <c r="T669" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U669" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="670" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A670" s="17" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B670" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C670" s="17">
+        <v>67840097</v>
+      </c>
+      <c r="D670" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E670" s="17">
+        <v>2722580585</v>
+      </c>
+      <c r="F670" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G670" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H670" s="18">
+        <v>46239</v>
+      </c>
+      <c r="I670" s="18">
+        <v>46289</v>
+      </c>
+      <c r="J670" s="8">
+        <f t="shared" si="30"/>
+        <v>37</v>
+      </c>
+      <c r="K670" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L670" s="65" t="s">
+        <v>318</v>
+      </c>
+      <c r="M670" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N670" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="O670" s="65">
+        <v>150000</v>
+      </c>
+      <c r="P670" s="65">
+        <v>60000</v>
+      </c>
+      <c r="Q670" s="67">
+        <v>210000</v>
+      </c>
+      <c r="R670" s="66">
+        <v>46289</v>
+      </c>
+      <c r="S670" s="8">
+        <f t="shared" si="32"/>
+        <v>37</v>
+      </c>
+      <c r="T670" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U670" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="671" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A671" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B671" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C671" s="17">
+        <v>66533655</v>
+      </c>
+      <c r="D671" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="E671" s="17" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F671" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G671" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H671" s="18">
+        <v>46217</v>
+      </c>
+      <c r="I671" s="18">
+        <v>46286</v>
+      </c>
+      <c r="J671" s="8">
+        <f t="shared" si="30"/>
+        <v>50</v>
+      </c>
+      <c r="K671" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L671" s="65" t="s">
+        <v>318</v>
+      </c>
+      <c r="M671" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N671" s="65" t="s">
+        <v>191</v>
+      </c>
+      <c r="O671" s="65">
+        <v>208139</v>
+      </c>
+      <c r="P671" s="65">
+        <v>165000</v>
+      </c>
+      <c r="Q671" s="67">
+        <v>373139</v>
+      </c>
+      <c r="R671" s="66">
+        <v>46290</v>
+      </c>
+      <c r="S671" s="8">
+        <f t="shared" si="32"/>
+        <v>54</v>
+      </c>
+      <c r="T671" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U671" s="65" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="672" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A672" s="17" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B672" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C672" s="17">
+        <v>66519778</v>
+      </c>
+      <c r="D672" s="17" t="s">
+        <v>594</v>
+      </c>
+      <c r="E672" s="17" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F672" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G672" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H672" s="18">
+        <v>46217</v>
+      </c>
+      <c r="I672" s="18">
+        <v>46289</v>
+      </c>
+      <c r="J672" s="8">
+        <f t="shared" si="30"/>
+        <v>53</v>
+      </c>
+      <c r="K672" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L672" s="65" t="s">
+        <v>318</v>
+      </c>
+      <c r="M672" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N672" s="65" t="s">
+        <v>191</v>
+      </c>
+      <c r="O672" s="65">
+        <v>821949</v>
+      </c>
+      <c r="P672" s="65">
+        <v>165000</v>
+      </c>
+      <c r="Q672" s="67">
+        <v>986949</v>
+      </c>
+      <c r="R672" s="66">
+        <v>46290</v>
+      </c>
+      <c r="S672" s="8">
+        <f t="shared" si="32"/>
+        <v>54</v>
+      </c>
+      <c r="T672" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U672" s="65" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="673" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A673" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B673" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C673" s="17">
+        <v>65835797</v>
+      </c>
+      <c r="D673" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="E673" s="17" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F673" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="G673" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H673" s="18">
+        <v>46205</v>
+      </c>
+      <c r="I673" s="18">
+        <v>46280</v>
+      </c>
+      <c r="J673" s="8">
+        <f t="shared" si="30"/>
+        <v>54</v>
+      </c>
+      <c r="K673" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="L673" s="65" t="s">
+        <v>318</v>
+      </c>
+      <c r="M673" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="N673" s="65" t="s">
+        <v>931</v>
+      </c>
+      <c r="O673" s="65">
+        <v>0</v>
+      </c>
+      <c r="P673" s="65">
+        <v>0</v>
+      </c>
+      <c r="Q673" s="67">
+        <v>0</v>
+      </c>
+      <c r="R673" s="66">
+        <v>46290</v>
+      </c>
+      <c r="S673" s="8">
+        <f t="shared" si="32"/>
+        <v>62</v>
+      </c>
+      <c r="T673" s="65" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U673" s="65" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="674" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A674" s="73" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B674" s="73" t="s">
+        <v>43</v>
+      </c>
+      <c r="C674" s="73">
+        <v>68982046</v>
+      </c>
+      <c r="D674" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="E674" s="73" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F674" s="73" t="s">
+        <v>46</v>
+      </c>
+      <c r="G674" s="73" t="s">
+        <v>37</v>
+      </c>
+      <c r="H674" s="74">
+        <v>46258</v>
+      </c>
+      <c r="I674" s="74">
+        <v>46279</v>
+      </c>
+      <c r="J674" s="8">
+        <f t="shared" si="30"/>
+        <v>16</v>
+      </c>
+      <c r="K674" s="76" t="s">
+        <v>295</v>
+      </c>
+      <c r="L674" s="75" t="s">
+        <v>296</v>
+      </c>
+      <c r="M674" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="N674" s="80" t="s">
+        <v>169</v>
+      </c>
+      <c r="O674" s="81">
+        <v>0</v>
+      </c>
+      <c r="P674" s="81">
+        <v>0</v>
+      </c>
+      <c r="Q674" s="81">
+        <f t="shared" ref="Q674" si="33">P674+O674</f>
+        <v>0</v>
+      </c>
+      <c r="R674" s="78">
+        <v>46290</v>
+      </c>
+      <c r="S674" s="8">
+        <f t="shared" si="32"/>
+        <v>25</v>
+      </c>
+      <c r="T674" s="75" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U674" s="75" t="s">
+        <v>537</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U665" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:U673" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="C1">
     <cfRule type="duplicateValues" dxfId="95" priority="90"/>
@@ -50327,10 +50979,10 @@
     <cfRule type="duplicateValues" dxfId="91" priority="96"/>
     <cfRule type="duplicateValues" dxfId="90" priority="95"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C435 C444:C650 C652:C1048576">
+  <conditionalFormatting sqref="C1:C435 C444:C650 C652:C673 C675:C1048576">
     <cfRule type="duplicateValues" dxfId="89" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C650 C652:C1048576">
+  <conditionalFormatting sqref="C1:C650 C652:C673 C675:C1048576">
     <cfRule type="duplicateValues" dxfId="88" priority="2"/>
     <cfRule type="duplicateValues" dxfId="87" priority="3"/>
     <cfRule type="duplicateValues" dxfId="86" priority="1"/>
@@ -50497,20 +51149,20 @@
   <conditionalFormatting sqref="C232:C242">
     <cfRule type="duplicateValues" dxfId="24" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C243:C286 C1:C204 C303:C328 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C1048576">
+  <conditionalFormatting sqref="C243:C286 C1:C204 C303:C328 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C673 C675:C1048576">
     <cfRule type="duplicateValues" dxfId="23" priority="184"/>
     <cfRule type="duplicateValues" dxfId="22" priority="185"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C243:C286 C1:C211 C303:C328 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C1048576">
+  <conditionalFormatting sqref="C243:C286 C1:C211 C303:C328 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C673 C675:C1048576">
     <cfRule type="duplicateValues" dxfId="21" priority="194"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C243:C286 C1:C231 C303:C328 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C1048576">
+  <conditionalFormatting sqref="C243:C286 C1:C231 C303:C328 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C673 C675:C1048576">
     <cfRule type="duplicateValues" dxfId="20" priority="199"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C303:C328 C1:C293 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C1048576">
+  <conditionalFormatting sqref="C303:C328 C1:C293 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C673 C675:C1048576">
     <cfRule type="duplicateValues" dxfId="19" priority="204"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C303:C328 C1:C294 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C1048576">
+  <conditionalFormatting sqref="C303:C328 C1:C294 C355:C356 C362:C369 C384:C395 C402:C435 C444:C650 C652:C673 C675:C1048576">
     <cfRule type="duplicateValues" dxfId="18" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C340:C346">
@@ -50522,10 +51174,10 @@
   <conditionalFormatting sqref="C383">
     <cfRule type="duplicateValues" dxfId="15" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C384:C395 C1:C369 C402:C435 C444:C650 C652:C1048576">
+  <conditionalFormatting sqref="C384:C395 C1:C369 C402:C435 C444:C650 C652:C673 C675:C1048576">
     <cfRule type="duplicateValues" dxfId="14" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C402:C435 C1:C395 C444:C650 C652:C1048576">
+  <conditionalFormatting sqref="C402:C435 C1:C395 C444:C650 C652:C673 C675:C1048576">
     <cfRule type="duplicateValues" dxfId="13" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
